--- a/ig/DM-JUIN-2026/CodeSystem-tre-r396-autorite.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-tre-r396-autorite.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="253">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>liste des autorités structurée en plusieurs types d'autorités : Ordres, ARS, ...</t>
+    <t>liste des autorités (autorités Ordres, autorités ARS, ...)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>49</t>
+    <t>84</t>
   </si>
   <si>
     <t>Code</t>
@@ -286,6 +286,30 @@
     <t>Structure</t>
   </si>
   <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Directions régionales de l'économie de l'emploi du travail et des solidarités</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Direction régionale et interdépartementale de l'Hébergement et du Logement</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Conseil départemental</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Direction Départementale de l'Emploi, du Travail et des Solidarités</t>
+  </si>
+  <si>
     <t>08</t>
   </si>
   <si>
@@ -557,6 +581,192 @@
   </si>
   <si>
     <t>Ordre des infirmiers</t>
+  </si>
+  <si>
+    <t>DREETS-01</t>
+  </si>
+  <si>
+    <t>DREETS-01 : Direction de l'économie de l'emploi du travail et des solidarités Guadeloupe</t>
+  </si>
+  <si>
+    <t>DREETS-02</t>
+  </si>
+  <si>
+    <t>DREETS-02 :  Direction de l'économie de l'emploi du travail et des solidarités Martinique</t>
+  </si>
+  <si>
+    <t>DREETS-03</t>
+  </si>
+  <si>
+    <t>DREETS-03 :  Direction générale cohésion et population Guyane</t>
+  </si>
+  <si>
+    <t>DREETS-05</t>
+  </si>
+  <si>
+    <t>DREETS-05 :  Direction de l'économie de l'emploi du travail et des solidarités de La Réunion</t>
+  </si>
+  <si>
+    <t>DREETS-06</t>
+  </si>
+  <si>
+    <t>DREETS-06 : Direction de l'économie de l'emploi du travail et des solidarités Mayotte</t>
+  </si>
+  <si>
+    <t>DREETS-11</t>
+  </si>
+  <si>
+    <t>DREETS-11 : Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités d'Ile de France</t>
+  </si>
+  <si>
+    <t>DREETS-24</t>
+  </si>
+  <si>
+    <t>DREETS-24 :  Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Centre-Val de Loire</t>
+  </si>
+  <si>
+    <t>DREETS-27</t>
+  </si>
+  <si>
+    <t>DREETS-27 :  Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Bourgogne-Franche-Comté</t>
+  </si>
+  <si>
+    <t>DREETS-28</t>
+  </si>
+  <si>
+    <t>DREETS-28 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Normandie</t>
+  </si>
+  <si>
+    <t>DREETS-32</t>
+  </si>
+  <si>
+    <t>DREETS-32 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Hauts-de-France</t>
+  </si>
+  <si>
+    <t>DREETS-44</t>
+  </si>
+  <si>
+    <t>DREETS-44 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Grand Est</t>
+  </si>
+  <si>
+    <t>DREETS-52</t>
+  </si>
+  <si>
+    <t>DREETS-52 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Pays de la Loire</t>
+  </si>
+  <si>
+    <t>DREETS-53</t>
+  </si>
+  <si>
+    <t>DREETS-53 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Bretagne</t>
+  </si>
+  <si>
+    <t>DREETS-75</t>
+  </si>
+  <si>
+    <t>DREETS-75 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Nouvelle-Aquitaine</t>
+  </si>
+  <si>
+    <t>DREETS-76</t>
+  </si>
+  <si>
+    <t>DREETS-76 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Occitanie</t>
+  </si>
+  <si>
+    <t>DREETS-84</t>
+  </si>
+  <si>
+    <t>DREETS-84 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Auvergne-Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>DREETS-93</t>
+  </si>
+  <si>
+    <t>DREETS-93 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités Provence-Alpes-Côte d'Azur</t>
+  </si>
+  <si>
+    <t>DREETS-94</t>
+  </si>
+  <si>
+    <t>DREETS-94 Direction régionale interdépartementale de l'économie de l'emploi du travail et des solidarités de Corse</t>
+  </si>
+  <si>
+    <t>DRHIL-11</t>
+  </si>
+  <si>
+    <t>DRHIL-11 : Direction régionale et interdépartementale de l'Hébergement et du Logement Ile de France</t>
+  </si>
+  <si>
+    <t>CD-01</t>
+  </si>
+  <si>
+    <t>CD-01 : Conseil départemental de l'Ain</t>
+  </si>
+  <si>
+    <t>CD-02</t>
+  </si>
+  <si>
+    <t>CD-02 : Conseil départemental del'Aisne</t>
+  </si>
+  <si>
+    <t>CD-03</t>
+  </si>
+  <si>
+    <t>CD-03 : Conseil départemental de l'Allier</t>
+  </si>
+  <si>
+    <t>CD-15</t>
+  </si>
+  <si>
+    <t>CD-15 : Conseil départemental du Cantal</t>
+  </si>
+  <si>
+    <t>CD-54</t>
+  </si>
+  <si>
+    <t>CD-54 : Conseil départemental de Meurthe et Moselle</t>
+  </si>
+  <si>
+    <t>CD-58</t>
+  </si>
+  <si>
+    <t>CD-58 : Conseil départemental de la Nièvre</t>
+  </si>
+  <si>
+    <t>CD-94</t>
+  </si>
+  <si>
+    <t>CD-94 : Conseil départemental du Val de Marne</t>
+  </si>
+  <si>
+    <t>CD-95</t>
+  </si>
+  <si>
+    <t>CD-95 : Conseil départemental du Val d'Oise</t>
+  </si>
+  <si>
+    <t>DDETS-01</t>
+  </si>
+  <si>
+    <t>DDETS-01 : Direction départementale de l'emploi, du travail et des solidarités Ain</t>
+  </si>
+  <si>
+    <t>DDETS-02</t>
+  </si>
+  <si>
+    <t>DDETS-02 : Direction départementale de l'emploi, du travail et des solidarités Aisne</t>
+  </si>
+  <si>
+    <t>DDETS-03</t>
+  </si>
+  <si>
+    <t>DDETS-03 : Direction départementale de l'emploi, du travail et des solidarités Allier</t>
+  </si>
+  <si>
+    <t>DDETS-95</t>
+  </si>
+  <si>
+    <t>DDETS-95 :Direction départementale de l'emploi, du travail et des solidarités Val d'Oise</t>
   </si>
   <si>
     <t>SSA</t>
@@ -1066,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1633,19 +1843,17 @@
       <c r="C47" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="D47" t="s" s="2">
-        <v>176</v>
-      </c>
+      <c r="D47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="B48" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="D48" s="2"/>
     </row>
@@ -1654,10 +1862,10 @@
         <v>83</v>
       </c>
       <c r="B49" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C49" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="D49" s="2"/>
     </row>
@@ -1666,12 +1874,434 @@
         <v>83</v>
       </c>
       <c r="B50" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C50" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="C50" t="s" s="2">
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="D50" s="2"/>
+      <c r="C51" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="D59" s="2"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="D60" s="2"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="D62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="D63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="D66" s="2"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="D69" s="2"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="D71" s="2"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="D74" s="2"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="D75" s="2"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="D76" s="2"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="D77" s="2"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="D79" s="2"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="D81" s="2"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="D82" s="2"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="D83" s="2"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="D84" s="2"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="D85" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
